--- a/tools/synthetic_pilots/synth_real_estate.xlsx
+++ b/tools/synthetic_pilots/synth_real_estate.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Данные" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>date</t>
   </si>
@@ -25,7 +25,7 @@
     <t>tv_spend</t>
   </si>
   <si>
-    <t>ooh_ots</t>
+    <t>ooh_contacts</t>
   </si>
   <si>
     <t>digital_spend</t>
@@ -34,19 +34,13 @@
     <t>performance_clicks</t>
   </si>
   <si>
-    <t>competitor_trp</t>
+    <t>competitor_activity</t>
   </si>
   <si>
-    <t>macro_cpi_monthly</t>
+    <t>macro_cpi</t>
   </si>
   <si>
-    <t>macro_cpi_cumulative</t>
-  </si>
-  <si>
-    <t>seasonality_q1</t>
-  </si>
-  <si>
-    <t>seasonality_q4</t>
+    <t>holiday_newyear</t>
   </si>
 </sst>
 </file>
@@ -382,10 +376,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,1270 +407,1048 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>44957</v>
       </c>
       <c r="B2">
-        <v>861</v>
+        <v>891</v>
       </c>
       <c r="C2">
-        <v>21291341</v>
+        <v>19723381</v>
       </c>
       <c r="D2">
-        <v>10969486</v>
+        <v>14483519</v>
       </c>
       <c r="E2">
-        <v>8675050</v>
+        <v>13631298</v>
       </c>
       <c r="F2">
-        <v>137021</v>
+        <v>193055</v>
       </c>
       <c r="G2">
-        <v>76.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="H2">
         <v>1.0241</v>
       </c>
       <c r="I2">
-        <v>1.0241</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>44985</v>
       </c>
       <c r="B3">
-        <v>845</v>
+        <v>902</v>
       </c>
       <c r="C3">
-        <v>22046793</v>
+        <v>25681093</v>
       </c>
       <c r="D3">
-        <v>10514898</v>
+        <v>8831902</v>
       </c>
       <c r="E3">
-        <v>15051011</v>
+        <v>24302645</v>
       </c>
       <c r="F3">
-        <v>178102</v>
+        <v>116661</v>
       </c>
       <c r="G3">
-        <v>113</v>
+        <v>128.5</v>
       </c>
       <c r="H3">
-        <v>1.0185</v>
+        <v>1.043</v>
       </c>
       <c r="I3">
-        <v>1.043</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>45016</v>
       </c>
       <c r="B4">
-        <v>862</v>
+        <v>970</v>
       </c>
       <c r="C4">
-        <v>31627741</v>
+        <v>45148512</v>
       </c>
       <c r="D4">
-        <v>8823990</v>
+        <v>13263727</v>
       </c>
       <c r="E4">
-        <v>8826086</v>
+        <v>11575320</v>
       </c>
       <c r="F4">
-        <v>176342</v>
+        <v>225771</v>
       </c>
       <c r="G4">
-        <v>90.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H4">
-        <v>1.0093</v>
+        <v>1.0527</v>
       </c>
       <c r="I4">
-        <v>1.0527</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>45046</v>
       </c>
       <c r="B5">
-        <v>873</v>
+        <v>908</v>
       </c>
       <c r="C5">
-        <v>42174216</v>
+        <v>43679266</v>
       </c>
       <c r="D5">
-        <v>21513371</v>
+        <v>25878827</v>
       </c>
       <c r="E5">
-        <v>7946766</v>
+        <v>6637405</v>
       </c>
       <c r="F5">
-        <v>77193</v>
+        <v>133363</v>
       </c>
       <c r="G5">
-        <v>80.8</v>
+        <v>65.8</v>
       </c>
       <c r="H5">
-        <v>1.0117</v>
+        <v>1.065</v>
       </c>
       <c r="I5">
-        <v>1.065</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>45077</v>
       </c>
       <c r="B6">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="C6">
-        <v>34668321</v>
+        <v>43336326</v>
       </c>
       <c r="D6">
-        <v>12347962</v>
+        <v>13977176</v>
       </c>
       <c r="E6">
-        <v>13640840</v>
+        <v>13108859</v>
       </c>
       <c r="F6">
-        <v>113561</v>
+        <v>106543</v>
       </c>
       <c r="G6">
-        <v>121.9</v>
+        <v>115.3</v>
       </c>
       <c r="H6">
-        <v>1.0021</v>
+        <v>1.0672</v>
       </c>
       <c r="I6">
-        <v>1.0672</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>45107</v>
       </c>
       <c r="B7">
-        <v>1069</v>
+        <v>1021</v>
       </c>
       <c r="C7">
-        <v>43874884</v>
+        <v>50803035</v>
       </c>
       <c r="D7">
-        <v>23271461</v>
+        <v>31973910</v>
       </c>
       <c r="E7">
-        <v>19195102</v>
+        <v>21401018</v>
       </c>
       <c r="F7">
-        <v>313952</v>
+        <v>186687</v>
       </c>
       <c r="G7">
-        <v>66.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H7">
-        <v>1.0167</v>
+        <v>1.085</v>
       </c>
       <c r="I7">
-        <v>1.085</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>45138</v>
       </c>
       <c r="B8">
-        <v>1014</v>
+        <v>990</v>
       </c>
       <c r="C8">
-        <v>32358999</v>
+        <v>16726352</v>
       </c>
       <c r="D8">
-        <v>20147941</v>
+        <v>19834007</v>
       </c>
       <c r="E8">
-        <v>13752918</v>
+        <v>13545059</v>
       </c>
       <c r="F8">
-        <v>211532</v>
+        <v>26372</v>
       </c>
       <c r="G8">
-        <v>112.1</v>
+        <v>91.5</v>
       </c>
       <c r="H8">
-        <v>1.0216</v>
+        <v>1.1085</v>
       </c>
       <c r="I8">
-        <v>1.1085</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>45169</v>
       </c>
       <c r="B9">
-        <v>1018</v>
+        <v>942</v>
       </c>
       <c r="C9">
-        <v>34059721</v>
+        <v>35680638</v>
       </c>
       <c r="D9">
-        <v>19144012</v>
+        <v>13776456</v>
       </c>
       <c r="E9">
-        <v>16799030</v>
+        <v>17883091</v>
       </c>
       <c r="F9">
-        <v>261028</v>
+        <v>155662</v>
       </c>
       <c r="G9">
-        <v>175.1</v>
+        <v>207.3</v>
       </c>
       <c r="H9">
-        <v>1.0134</v>
+        <v>1.1234</v>
       </c>
       <c r="I9">
-        <v>1.1234</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>45199</v>
       </c>
       <c r="B10">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="C10">
-        <v>28013542</v>
+        <v>40869697</v>
       </c>
       <c r="D10">
-        <v>7787147</v>
+        <v>5867589</v>
       </c>
       <c r="E10">
-        <v>18742116</v>
+        <v>22208301</v>
       </c>
       <c r="F10">
-        <v>381344</v>
+        <v>294090</v>
       </c>
       <c r="G10">
-        <v>44.9</v>
+        <v>49.3</v>
       </c>
       <c r="H10">
-        <v>1.0161</v>
+        <v>1.1415</v>
       </c>
       <c r="I10">
-        <v>1.1415</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>45230</v>
       </c>
       <c r="B11">
-        <v>1086</v>
+        <v>1061</v>
       </c>
       <c r="C11">
-        <v>41102704</v>
+        <v>46497631</v>
       </c>
       <c r="D11">
-        <v>15051842</v>
+        <v>15255756</v>
       </c>
       <c r="E11">
-        <v>16900587</v>
+        <v>7506552</v>
       </c>
       <c r="F11">
-        <v>317550</v>
+        <v>272774</v>
       </c>
       <c r="G11">
-        <v>85.8</v>
+        <v>73</v>
       </c>
       <c r="H11">
-        <v>1.0089</v>
+        <v>1.1517</v>
       </c>
       <c r="I11">
-        <v>1.1517</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>45260</v>
       </c>
       <c r="B12">
-        <v>949</v>
+        <v>979</v>
       </c>
       <c r="C12">
-        <v>31239034</v>
+        <v>18427286</v>
       </c>
       <c r="D12">
-        <v>23272396</v>
+        <v>15140459</v>
       </c>
       <c r="E12">
-        <v>7320680</v>
+        <v>6210934</v>
       </c>
       <c r="F12">
-        <v>108652</v>
+        <v>192868</v>
       </c>
       <c r="G12">
-        <v>106.7</v>
+        <v>103</v>
       </c>
       <c r="H12">
-        <v>1.015</v>
+        <v>1.1689</v>
       </c>
       <c r="I12">
-        <v>1.1689</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>45291</v>
       </c>
       <c r="B13">
-        <v>1005</v>
+        <v>969</v>
       </c>
       <c r="C13">
-        <v>45559201</v>
+        <v>35092238</v>
       </c>
       <c r="D13">
-        <v>26432109</v>
+        <v>27854695</v>
       </c>
       <c r="E13">
-        <v>15865095</v>
+        <v>13593679</v>
       </c>
       <c r="F13">
-        <v>115402</v>
+        <v>112559</v>
       </c>
       <c r="G13">
-        <v>79.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H13">
-        <v>1.0102</v>
+        <v>1.1808</v>
       </c>
       <c r="I13">
-        <v>1.1808</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>45322</v>
       </c>
       <c r="B14">
-        <v>907</v>
+        <v>849</v>
       </c>
       <c r="C14">
-        <v>25961403</v>
+        <v>26663816</v>
       </c>
       <c r="D14">
-        <v>10715079</v>
+        <v>9506995</v>
       </c>
       <c r="E14">
-        <v>11706986</v>
+        <v>12855939</v>
       </c>
       <c r="F14">
-        <v>109719</v>
+        <v>47422</v>
       </c>
       <c r="G14">
-        <v>91.2</v>
+        <v>87.5</v>
       </c>
       <c r="H14">
-        <v>1.0165</v>
+        <v>1.2003</v>
       </c>
       <c r="I14">
-        <v>1.2003</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>45351</v>
       </c>
       <c r="B15">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="C15">
-        <v>23654626</v>
+        <v>31673561</v>
       </c>
       <c r="D15">
-        <v>18820037</v>
+        <v>24097832</v>
       </c>
       <c r="E15">
-        <v>10888219</v>
+        <v>15127198</v>
       </c>
       <c r="F15">
-        <v>131924</v>
+        <v>119944</v>
       </c>
       <c r="G15">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="H15">
-        <v>1.0068</v>
+        <v>1.2085</v>
       </c>
       <c r="I15">
-        <v>1.2085</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>45382</v>
       </c>
       <c r="B16">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C16">
-        <v>39025863</v>
+        <v>58862373</v>
       </c>
       <c r="D16">
-        <v>6929420</v>
+        <v>6109597</v>
       </c>
       <c r="E16">
-        <v>11094385</v>
+        <v>11206050</v>
       </c>
       <c r="F16">
-        <v>59716</v>
+        <v>83241</v>
       </c>
       <c r="G16">
-        <v>84.8</v>
+        <v>104.5</v>
       </c>
       <c r="H16">
-        <v>1.0102</v>
+        <v>1.2208</v>
       </c>
       <c r="I16">
-        <v>1.2208</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>45412</v>
       </c>
       <c r="B17">
-        <v>877</v>
+        <v>893</v>
       </c>
       <c r="C17">
-        <v>29513430</v>
+        <v>31511292</v>
       </c>
       <c r="D17">
-        <v>16033180</v>
+        <v>23273417</v>
       </c>
       <c r="E17">
-        <v>13972335</v>
+        <v>12133607</v>
       </c>
       <c r="F17">
-        <v>228226</v>
+        <v>129228</v>
       </c>
       <c r="G17">
-        <v>140.1</v>
+        <v>157</v>
       </c>
       <c r="H17">
-        <v>1.0084</v>
+        <v>1.2311</v>
       </c>
       <c r="I17">
-        <v>1.2311</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>45443</v>
       </c>
       <c r="B18">
-        <v>945</v>
+        <v>973</v>
       </c>
       <c r="C18">
-        <v>36132250</v>
+        <v>26457584</v>
       </c>
       <c r="D18">
-        <v>17196847</v>
+        <v>25466514</v>
       </c>
       <c r="E18">
-        <v>10582866</v>
+        <v>9287480</v>
       </c>
       <c r="F18">
-        <v>135820</v>
+        <v>153168</v>
       </c>
       <c r="G18">
-        <v>32.4</v>
+        <v>25.6</v>
       </c>
       <c r="H18">
-        <v>1.0156</v>
+        <v>1.2502</v>
       </c>
       <c r="I18">
-        <v>1.2502</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>45473</v>
       </c>
       <c r="B19">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="C19">
-        <v>45634829</v>
+        <v>49815846</v>
       </c>
       <c r="D19">
-        <v>9168014</v>
+        <v>9321642</v>
       </c>
       <c r="E19">
-        <v>20382767</v>
+        <v>26407776</v>
       </c>
       <c r="F19">
-        <v>405974</v>
+        <v>255669</v>
       </c>
       <c r="G19">
-        <v>94.59999999999999</v>
+        <v>121.5</v>
       </c>
       <c r="H19">
-        <v>0.9997</v>
+        <v>1.2499</v>
       </c>
       <c r="I19">
-        <v>1.2499</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>45504</v>
       </c>
       <c r="B20">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C20">
-        <v>33669393</v>
+        <v>32109261</v>
       </c>
       <c r="D20">
-        <v>9232101</v>
+        <v>8041985</v>
       </c>
       <c r="E20">
-        <v>9622551</v>
+        <v>6660379</v>
       </c>
       <c r="F20">
-        <v>174129</v>
+        <v>235724</v>
       </c>
       <c r="G20">
-        <v>61.8</v>
+        <v>82</v>
       </c>
       <c r="H20">
-        <v>1.0219</v>
+        <v>1.2772</v>
       </c>
       <c r="I20">
-        <v>1.2772</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>45535</v>
       </c>
       <c r="B21">
-        <v>972</v>
+        <v>944</v>
       </c>
       <c r="C21">
-        <v>13434352</v>
+        <v>15100049</v>
       </c>
       <c r="D21">
-        <v>17076728</v>
+        <v>13464729</v>
       </c>
       <c r="E21">
-        <v>15192762</v>
+        <v>14039436</v>
       </c>
       <c r="F21">
-        <v>266688</v>
+        <v>244166</v>
       </c>
       <c r="G21">
-        <v>61.5</v>
+        <v>62.4</v>
       </c>
       <c r="H21">
-        <v>1.0229</v>
+        <v>1.3064</v>
       </c>
       <c r="I21">
-        <v>1.3064</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>45565</v>
       </c>
       <c r="B22">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C22">
-        <v>12139779</v>
+        <v>14095863</v>
       </c>
       <c r="D22">
-        <v>5062826</v>
+        <v>4463050</v>
       </c>
       <c r="E22">
-        <v>9936902</v>
+        <v>11414262</v>
       </c>
       <c r="F22">
-        <v>81769</v>
+        <v>68389</v>
       </c>
       <c r="G22">
-        <v>115.3</v>
+        <v>126.5</v>
       </c>
       <c r="H22">
-        <v>1.0102</v>
+        <v>1.3197</v>
       </c>
       <c r="I22">
-        <v>1.3197</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>45596</v>
       </c>
       <c r="B23">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="C23">
-        <v>17364343</v>
+        <v>19525043</v>
       </c>
       <c r="D23">
-        <v>13264896</v>
+        <v>7271909</v>
       </c>
       <c r="E23">
-        <v>13132070</v>
+        <v>12356839</v>
       </c>
       <c r="F23">
-        <v>257500</v>
+        <v>164405</v>
       </c>
       <c r="G23">
-        <v>51.3</v>
+        <v>42.2</v>
       </c>
       <c r="H23">
-        <v>1.0034</v>
+        <v>1.3242</v>
       </c>
       <c r="I23">
-        <v>1.3242</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>45626</v>
       </c>
       <c r="B24">
-        <v>856</v>
+        <v>803</v>
       </c>
       <c r="C24">
-        <v>41197054</v>
+        <v>43980264</v>
       </c>
       <c r="D24">
-        <v>11782664</v>
+        <v>7716133</v>
       </c>
       <c r="E24">
-        <v>16280247</v>
+        <v>9346495</v>
       </c>
       <c r="F24">
-        <v>117063</v>
+        <v>81713</v>
       </c>
       <c r="G24">
-        <v>138.2</v>
+        <v>164.3</v>
       </c>
       <c r="H24">
-        <v>1.0224</v>
+        <v>1.3539</v>
       </c>
       <c r="I24">
-        <v>1.3539</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>45657</v>
       </c>
       <c r="B25">
-        <v>982</v>
+        <v>890</v>
       </c>
       <c r="C25">
-        <v>13525396</v>
+        <v>10728200</v>
       </c>
       <c r="D25">
-        <v>27250478</v>
+        <v>27313951</v>
       </c>
       <c r="E25">
-        <v>19428829</v>
+        <v>16476886</v>
       </c>
       <c r="F25">
-        <v>324170</v>
+        <v>205312</v>
       </c>
       <c r="G25">
-        <v>134.7</v>
+        <v>120.3</v>
       </c>
       <c r="H25">
-        <v>1.0137</v>
+        <v>1.3724</v>
       </c>
       <c r="I25">
-        <v>1.3724</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>45688</v>
       </c>
       <c r="B26">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="C26">
-        <v>31726991</v>
+        <v>49961740</v>
       </c>
       <c r="D26">
-        <v>10346597</v>
+        <v>11074786</v>
       </c>
       <c r="E26">
-        <v>5300966</v>
+        <v>3452301</v>
       </c>
       <c r="F26">
-        <v>44522</v>
+        <v>75903</v>
       </c>
       <c r="G26">
-        <v>92.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H26">
-        <v>1.0106</v>
+        <v>1.387</v>
       </c>
       <c r="I26">
-        <v>1.387</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>45716</v>
       </c>
       <c r="B27">
-        <v>864</v>
+        <v>909</v>
       </c>
       <c r="C27">
-        <v>21484907</v>
+        <v>31177119</v>
       </c>
       <c r="D27">
-        <v>18427380</v>
+        <v>22281231</v>
       </c>
       <c r="E27">
-        <v>15250078</v>
+        <v>22178751</v>
       </c>
       <c r="F27">
-        <v>187199</v>
+        <v>123592</v>
       </c>
       <c r="G27">
-        <v>51.4</v>
+        <v>53.8</v>
       </c>
       <c r="H27">
-        <v>1.0112</v>
+        <v>1.4025</v>
       </c>
       <c r="I27">
-        <v>1.4025</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>45747</v>
       </c>
       <c r="B28">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="C28">
-        <v>19080400</v>
+        <v>25695478</v>
       </c>
       <c r="D28">
-        <v>19668861</v>
+        <v>30142939</v>
       </c>
       <c r="E28">
-        <v>5755819</v>
+        <v>8125118</v>
       </c>
       <c r="F28">
-        <v>63559</v>
+        <v>148710</v>
       </c>
       <c r="G28">
-        <v>103.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H28">
-        <v>1.0118</v>
+        <v>1.419</v>
       </c>
       <c r="I28">
-        <v>1.419</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>45777</v>
       </c>
       <c r="B29">
-        <v>911</v>
+        <v>937</v>
       </c>
       <c r="C29">
-        <v>13882236</v>
+        <v>8888772</v>
       </c>
       <c r="D29">
-        <v>9515070</v>
+        <v>12286274</v>
       </c>
       <c r="E29">
-        <v>15275486</v>
+        <v>12594879</v>
       </c>
       <c r="F29">
-        <v>305209</v>
+        <v>270213</v>
       </c>
       <c r="G29">
-        <v>43.1</v>
+        <v>35.7</v>
       </c>
       <c r="H29">
-        <v>1.0192</v>
+        <v>1.4463</v>
       </c>
       <c r="I29">
-        <v>1.4463</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>45808</v>
       </c>
       <c r="B30">
-        <v>858</v>
+        <v>880</v>
       </c>
       <c r="C30">
-        <v>13371862</v>
+        <v>10759328</v>
       </c>
       <c r="D30">
-        <v>24399070</v>
+        <v>29701490</v>
       </c>
       <c r="E30">
-        <v>10240392</v>
+        <v>7190667</v>
       </c>
       <c r="F30">
-        <v>111803</v>
+        <v>139370</v>
       </c>
       <c r="G30">
-        <v>85.5</v>
+        <v>64.5</v>
       </c>
       <c r="H30">
-        <v>1.0119</v>
+        <v>1.4634</v>
       </c>
       <c r="I30">
-        <v>1.4634</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>45838</v>
       </c>
       <c r="B31">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C31">
-        <v>15092373</v>
+        <v>14343794</v>
       </c>
       <c r="D31">
-        <v>19313795</v>
+        <v>21647205</v>
       </c>
       <c r="E31">
-        <v>12132525</v>
+        <v>11716173</v>
       </c>
       <c r="F31">
-        <v>300618</v>
+        <v>346232</v>
       </c>
       <c r="G31">
-        <v>33.9</v>
+        <v>44.2</v>
       </c>
       <c r="H31">
-        <v>1.0125</v>
+        <v>1.4817</v>
       </c>
       <c r="I31">
-        <v>1.4817</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>45869</v>
       </c>
       <c r="B32">
-        <v>809</v>
+        <v>792</v>
       </c>
       <c r="C32">
-        <v>41250797</v>
+        <v>43412700</v>
       </c>
       <c r="D32">
-        <v>8002001</v>
+        <v>8176314</v>
       </c>
       <c r="E32">
-        <v>13076624</v>
+        <v>10242010</v>
       </c>
       <c r="F32">
-        <v>123955</v>
+        <v>120664</v>
       </c>
       <c r="G32">
-        <v>103.4</v>
+        <v>147.4</v>
       </c>
       <c r="H32">
-        <v>1.0145</v>
+        <v>1.5031</v>
       </c>
       <c r="I32">
-        <v>1.5031</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>45900</v>
       </c>
       <c r="B33">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="C33">
-        <v>13963069</v>
+        <v>7674164</v>
       </c>
       <c r="D33">
-        <v>8026539</v>
+        <v>8089171</v>
       </c>
       <c r="E33">
-        <v>10018927</v>
+        <v>7173286</v>
       </c>
       <c r="F33">
-        <v>71147</v>
+        <v>119736</v>
       </c>
       <c r="G33">
-        <v>28.9</v>
+        <v>30.5</v>
       </c>
       <c r="H33">
-        <v>1.0136</v>
+        <v>1.5235</v>
       </c>
       <c r="I33">
-        <v>1.5235</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>45930</v>
       </c>
       <c r="B34">
-        <v>844</v>
+        <v>804</v>
       </c>
       <c r="C34">
-        <v>39482115</v>
+        <v>56062693</v>
       </c>
       <c r="D34">
-        <v>14864193</v>
+        <v>14471195</v>
       </c>
       <c r="E34">
-        <v>18975170</v>
+        <v>18428522</v>
       </c>
       <c r="F34">
-        <v>113234</v>
+        <v>83319</v>
       </c>
       <c r="G34">
-        <v>141.8</v>
+        <v>157.3</v>
       </c>
       <c r="H34">
-        <v>1.0066</v>
+        <v>1.5336</v>
       </c>
       <c r="I34">
-        <v>1.5336</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>45961</v>
       </c>
       <c r="B35">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="C35">
-        <v>36647556</v>
+        <v>29233847</v>
       </c>
       <c r="D35">
-        <v>19806729</v>
+        <v>20491695</v>
       </c>
       <c r="E35">
-        <v>12417904</v>
+        <v>12543711</v>
       </c>
       <c r="F35">
-        <v>245621</v>
+        <v>237808</v>
       </c>
       <c r="G35">
-        <v>87.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H35">
-        <v>1.0134</v>
+        <v>1.5542</v>
       </c>
       <c r="I35">
-        <v>1.5542</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>45991</v>
       </c>
       <c r="B36">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="C36">
-        <v>29679671</v>
+        <v>22876247</v>
       </c>
       <c r="D36">
-        <v>34284277</v>
+        <v>36531266</v>
       </c>
       <c r="E36">
-        <v>7165520</v>
+        <v>5286902</v>
       </c>
       <c r="F36">
-        <v>53833</v>
+        <v>91838</v>
       </c>
       <c r="G36">
-        <v>43.2</v>
+        <v>44.9</v>
       </c>
       <c r="H36">
-        <v>1.0059</v>
+        <v>1.5634</v>
       </c>
       <c r="I36">
-        <v>1.5634</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>46022</v>
       </c>
       <c r="B37">
-        <v>988</v>
+        <v>935</v>
       </c>
       <c r="C37">
-        <v>57561447</v>
+        <v>56675872</v>
       </c>
       <c r="D37">
-        <v>7877899</v>
+        <v>2265850</v>
       </c>
       <c r="E37">
-        <v>18350477</v>
+        <v>11850729</v>
       </c>
       <c r="F37">
-        <v>121593</v>
+        <v>98989</v>
       </c>
       <c r="G37">
-        <v>22.7</v>
+        <v>21.3</v>
       </c>
       <c r="H37">
-        <v>1.0161</v>
+        <v>1.5886</v>
       </c>
       <c r="I37">
-        <v>1.5886</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
         <v>1</v>
       </c>
     </row>

--- a/tools/synthetic_pilots/synth_real_estate.xlsx
+++ b/tools/synthetic_pilots/synth_real_estate.xlsx
@@ -431,31 +431,31 @@
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>3706</v>
+        <v>3119</v>
       </c>
       <c r="C2">
-        <v>23359946</v>
+        <v>29844516</v>
       </c>
       <c r="D2">
-        <v>151.3</v>
+        <v>193.3</v>
       </c>
       <c r="E2">
-        <v>4272798</v>
+        <v>5519852</v>
       </c>
       <c r="F2">
-        <v>50248717</v>
+        <v>64914262</v>
       </c>
       <c r="G2">
-        <v>17125271</v>
+        <v>14250737</v>
       </c>
       <c r="H2">
-        <v>83290572</v>
+        <v>69309972</v>
       </c>
       <c r="I2">
-        <v>5100651</v>
+        <v>2059720</v>
       </c>
       <c r="J2">
-        <v>56383</v>
+        <v>22768</v>
       </c>
       <c r="K2">
         <v>22.5</v>
@@ -469,31 +469,31 @@
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>4406</v>
+        <v>3472</v>
       </c>
       <c r="C3">
-        <v>30915790</v>
+        <v>39553551</v>
       </c>
       <c r="D3">
-        <v>211.2</v>
+        <v>270.2</v>
       </c>
       <c r="E3">
-        <v>9947053</v>
+        <v>12675896</v>
       </c>
       <c r="F3">
-        <v>118996924</v>
+        <v>151642163</v>
       </c>
       <c r="G3">
-        <v>28089432</v>
+        <v>23397686</v>
       </c>
       <c r="H3">
-        <v>138914293</v>
+        <v>115711596</v>
       </c>
       <c r="I3">
-        <v>23547213</v>
+        <v>9266314</v>
       </c>
       <c r="J3">
-        <v>272071</v>
+        <v>107065</v>
       </c>
       <c r="K3">
         <v>140.8</v>
@@ -507,31 +507,31 @@
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>4045</v>
+        <v>3406</v>
       </c>
       <c r="C4">
-        <v>50040948</v>
+        <v>63633078</v>
       </c>
       <c r="D4">
-        <v>329.6</v>
+        <v>419.1</v>
       </c>
       <c r="E4">
-        <v>3772359</v>
+        <v>4858537</v>
       </c>
       <c r="F4">
-        <v>49783290</v>
+        <v>64117439</v>
       </c>
       <c r="G4">
-        <v>10336121</v>
+        <v>8559538</v>
       </c>
       <c r="H4">
-        <v>52225142</v>
+        <v>43248632</v>
       </c>
       <c r="I4">
-        <v>5993470</v>
+        <v>2373877</v>
       </c>
       <c r="J4">
-        <v>65663</v>
+        <v>26007</v>
       </c>
       <c r="K4">
         <v>115.9</v>
@@ -545,31 +545,31 @@
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>3519</v>
+        <v>3122</v>
       </c>
       <c r="C5">
-        <v>909906</v>
+        <v>1155981</v>
       </c>
       <c r="D5">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="E5">
-        <v>4498922</v>
+        <v>5858517</v>
       </c>
       <c r="F5">
-        <v>55001876</v>
+        <v>71623698</v>
       </c>
       <c r="G5">
-        <v>12330192</v>
+        <v>10225457</v>
       </c>
       <c r="H5">
-        <v>62490670</v>
+        <v>51823657</v>
       </c>
       <c r="I5">
-        <v>305317</v>
+        <v>120540</v>
       </c>
       <c r="J5">
-        <v>3323</v>
+        <v>1312</v>
       </c>
       <c r="K5">
         <v>13.1</v>
@@ -583,31 +583,31 @@
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>3971</v>
+        <v>3297</v>
       </c>
       <c r="C6">
-        <v>19397298</v>
+        <v>24832268</v>
       </c>
       <c r="D6">
-        <v>128.1</v>
+        <v>164</v>
       </c>
       <c r="E6">
-        <v>7504019</v>
+        <v>9617752</v>
       </c>
       <c r="F6">
-        <v>91908112</v>
+        <v>117796795</v>
       </c>
       <c r="G6">
-        <v>21581290</v>
+        <v>17889057</v>
       </c>
       <c r="H6">
-        <v>104730640</v>
+        <v>86812812</v>
       </c>
       <c r="I6">
-        <v>12731130</v>
+        <v>5074084</v>
       </c>
       <c r="J6">
-        <v>143436</v>
+        <v>57167</v>
       </c>
       <c r="K6">
         <v>73.09999999999999</v>
@@ -621,31 +621,31 @@
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>4148</v>
+        <v>3459</v>
       </c>
       <c r="C7">
-        <v>48430409</v>
+        <v>61565865</v>
       </c>
       <c r="D7">
-        <v>307.4</v>
+        <v>390.8</v>
       </c>
       <c r="E7">
-        <v>13002235</v>
+        <v>16563116</v>
       </c>
       <c r="F7">
-        <v>163985501</v>
+        <v>208895693</v>
       </c>
       <c r="G7">
-        <v>17266567</v>
+        <v>14289449</v>
       </c>
       <c r="H7">
-        <v>86006945</v>
+        <v>71177547</v>
       </c>
       <c r="I7">
-        <v>13738381</v>
+        <v>5488610</v>
       </c>
       <c r="J7">
-        <v>153802</v>
+        <v>61445</v>
       </c>
       <c r="K7">
         <v>138</v>
@@ -659,31 +659,31 @@
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>4284</v>
+        <v>3458</v>
       </c>
       <c r="C8">
-        <v>773929</v>
+        <v>983518</v>
       </c>
       <c r="D8">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="E8">
-        <v>87268</v>
+        <v>111852</v>
       </c>
       <c r="F8">
-        <v>1042320</v>
+        <v>1335954</v>
       </c>
       <c r="G8">
-        <v>165983</v>
+        <v>137994</v>
       </c>
       <c r="H8">
-        <v>893720</v>
+        <v>743015</v>
       </c>
       <c r="I8">
-        <v>20302707</v>
+        <v>8005264</v>
       </c>
       <c r="J8">
-        <v>236663</v>
+        <v>93315</v>
       </c>
       <c r="K8">
         <v>88.8</v>
@@ -697,31 +697,31 @@
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>4559</v>
+        <v>3622</v>
       </c>
       <c r="C9">
-        <v>797023</v>
+        <v>1017627</v>
       </c>
       <c r="D9">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="E9">
-        <v>142843</v>
+        <v>182375</v>
       </c>
       <c r="F9">
-        <v>1794490</v>
+        <v>2291108</v>
       </c>
       <c r="G9">
-        <v>11131973</v>
+        <v>9144901</v>
       </c>
       <c r="H9">
-        <v>57227029</v>
+        <v>47011928</v>
       </c>
       <c r="I9">
-        <v>23963575</v>
+        <v>9460583</v>
       </c>
       <c r="J9">
-        <v>264555</v>
+        <v>104444</v>
       </c>
       <c r="K9">
         <v>52.6</v>
@@ -735,31 +735,31 @@
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>4270</v>
+        <v>3677</v>
       </c>
       <c r="C10">
-        <v>28802592</v>
+        <v>37022398</v>
       </c>
       <c r="D10">
-        <v>191.8</v>
+        <v>246.5</v>
       </c>
       <c r="E10">
-        <v>208052</v>
+        <v>265302</v>
       </c>
       <c r="F10">
-        <v>2589949</v>
+        <v>3302628</v>
       </c>
       <c r="G10">
-        <v>23915844</v>
+        <v>19922382</v>
       </c>
       <c r="H10">
-        <v>117274925</v>
+        <v>97692384</v>
       </c>
       <c r="I10">
-        <v>85073</v>
+        <v>34002</v>
       </c>
       <c r="J10">
-        <v>937</v>
+        <v>374</v>
       </c>
       <c r="K10">
         <v>63.6</v>
@@ -773,31 +773,31 @@
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>4802</v>
+        <v>4120</v>
       </c>
       <c r="C11">
-        <v>49008099</v>
+        <v>62447095</v>
       </c>
       <c r="D11">
-        <v>307.3</v>
+        <v>391.5</v>
       </c>
       <c r="E11">
-        <v>9754595</v>
+        <v>12435608</v>
       </c>
       <c r="F11">
-        <v>119213871</v>
+        <v>151979356</v>
       </c>
       <c r="G11">
-        <v>18217649</v>
+        <v>15166778</v>
       </c>
       <c r="H11">
-        <v>90162904</v>
+        <v>75063514</v>
       </c>
       <c r="I11">
-        <v>9151511</v>
+        <v>3695863</v>
       </c>
       <c r="J11">
-        <v>102494</v>
+        <v>41392</v>
       </c>
       <c r="K11">
         <v>46</v>
@@ -811,31 +811,31 @@
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>5197</v>
+        <v>4270</v>
       </c>
       <c r="C12">
-        <v>42188973</v>
+        <v>53817786</v>
       </c>
       <c r="D12">
-        <v>271.2</v>
+        <v>345.9</v>
       </c>
       <c r="E12">
-        <v>39794</v>
+        <v>52466</v>
       </c>
       <c r="F12">
-        <v>452123</v>
+        <v>596099</v>
       </c>
       <c r="G12">
-        <v>9619414</v>
+        <v>7820582</v>
       </c>
       <c r="H12">
-        <v>45452831</v>
+        <v>36953148</v>
       </c>
       <c r="I12">
-        <v>28674665</v>
+        <v>11310574</v>
       </c>
       <c r="J12">
-        <v>298588</v>
+        <v>117776</v>
       </c>
       <c r="K12">
         <v>64.40000000000001</v>
@@ -849,31 +849,31 @@
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>4733</v>
+        <v>3927</v>
       </c>
       <c r="C13">
-        <v>737230</v>
+        <v>936128</v>
       </c>
       <c r="D13">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="E13">
-        <v>142247</v>
+        <v>182267</v>
       </c>
       <c r="F13">
-        <v>1633820</v>
+        <v>2093487</v>
       </c>
       <c r="G13">
-        <v>170948</v>
+        <v>141416</v>
       </c>
       <c r="H13">
-        <v>832263</v>
+        <v>688483</v>
       </c>
       <c r="I13">
-        <v>10507877</v>
+        <v>4214981</v>
       </c>
       <c r="J13">
-        <v>113258</v>
+        <v>45431</v>
       </c>
       <c r="K13">
         <v>88.3</v>
@@ -887,31 +887,31 @@
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>4238</v>
+        <v>3611</v>
       </c>
       <c r="C14">
-        <v>1101525</v>
+        <v>1401881</v>
       </c>
       <c r="D14">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E14">
-        <v>3547437</v>
+        <v>4529388</v>
       </c>
       <c r="F14">
-        <v>41382591</v>
+        <v>52837540</v>
       </c>
       <c r="G14">
-        <v>24162596</v>
+        <v>20023330</v>
       </c>
       <c r="H14">
-        <v>117857553</v>
+        <v>97667513</v>
       </c>
       <c r="I14">
-        <v>5206098</v>
+        <v>2113274</v>
       </c>
       <c r="J14">
-        <v>58596</v>
+        <v>23786</v>
       </c>
       <c r="K14">
         <v>148.8</v>
@@ -925,31 +925,31 @@
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>4367</v>
+        <v>3708</v>
       </c>
       <c r="C15">
-        <v>36624828</v>
+        <v>46856851</v>
       </c>
       <c r="D15">
-        <v>240.2</v>
+        <v>307.3</v>
       </c>
       <c r="E15">
-        <v>8457206</v>
+        <v>10837150</v>
       </c>
       <c r="F15">
-        <v>98455117</v>
+        <v>126161399</v>
       </c>
       <c r="G15">
-        <v>8590108</v>
+        <v>7053628</v>
       </c>
       <c r="H15">
-        <v>38340119</v>
+        <v>31482370</v>
       </c>
       <c r="I15">
-        <v>10593181</v>
+        <v>4165638</v>
       </c>
       <c r="J15">
-        <v>110591</v>
+        <v>43489</v>
       </c>
       <c r="K15">
         <v>49.1</v>
@@ -963,31 +963,31 @@
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>3791</v>
+        <v>3463</v>
       </c>
       <c r="C16">
-        <v>52476004</v>
+        <v>66502798</v>
       </c>
       <c r="D16">
-        <v>326.8</v>
+        <v>414.2</v>
       </c>
       <c r="E16">
-        <v>9021185</v>
+        <v>11525606</v>
       </c>
       <c r="F16">
-        <v>107279526</v>
+        <v>137061982</v>
       </c>
       <c r="G16">
-        <v>8422650</v>
+        <v>6980054</v>
       </c>
       <c r="H16">
-        <v>40826741</v>
+        <v>33834109</v>
       </c>
       <c r="I16">
-        <v>203092</v>
+        <v>80616</v>
       </c>
       <c r="J16">
-        <v>2284</v>
+        <v>906</v>
       </c>
       <c r="K16">
         <v>62.5</v>
@@ -1001,31 +1001,31 @@
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>3491</v>
+        <v>3199</v>
       </c>
       <c r="C17">
-        <v>329284</v>
+        <v>422188</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E17">
-        <v>7330560</v>
+        <v>9382034</v>
       </c>
       <c r="F17">
-        <v>89865376</v>
+        <v>115014407</v>
       </c>
       <c r="G17">
-        <v>12617197</v>
+        <v>10427735</v>
       </c>
       <c r="H17">
-        <v>59277542</v>
+        <v>48991114</v>
       </c>
       <c r="I17">
-        <v>240032</v>
+        <v>96118</v>
       </c>
       <c r="J17">
-        <v>2637</v>
+        <v>1056</v>
       </c>
       <c r="K17">
         <v>43.6</v>
@@ -1039,31 +1039,31 @@
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>3486</v>
+        <v>3169</v>
       </c>
       <c r="C18">
-        <v>32171931</v>
+        <v>40872977</v>
       </c>
       <c r="D18">
-        <v>200.7</v>
+        <v>255</v>
       </c>
       <c r="E18">
-        <v>4716566</v>
+        <v>6082796</v>
       </c>
       <c r="F18">
-        <v>55141789</v>
+        <v>71114501</v>
       </c>
       <c r="G18">
-        <v>3548807</v>
+        <v>2922749</v>
       </c>
       <c r="H18">
-        <v>16962458</v>
+        <v>13970046</v>
       </c>
       <c r="I18">
-        <v>4152551</v>
+        <v>1725067</v>
       </c>
       <c r="J18">
-        <v>43280</v>
+        <v>17979</v>
       </c>
       <c r="K18">
         <v>37.8</v>
@@ -1077,31 +1077,31 @@
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>3759</v>
+        <v>3324</v>
       </c>
       <c r="C19">
-        <v>43726957</v>
+        <v>55500061</v>
       </c>
       <c r="D19">
-        <v>267.8</v>
+        <v>339.9</v>
       </c>
       <c r="E19">
-        <v>8908311</v>
+        <v>11351535</v>
       </c>
       <c r="F19">
-        <v>105008121</v>
+        <v>133808009</v>
       </c>
       <c r="G19">
-        <v>10092049</v>
+        <v>8384606</v>
       </c>
       <c r="H19">
-        <v>48483982</v>
+        <v>40281123</v>
       </c>
       <c r="I19">
-        <v>7787928</v>
+        <v>3137352</v>
       </c>
       <c r="J19">
-        <v>83764</v>
+        <v>33744</v>
       </c>
       <c r="K19">
         <v>83.5</v>
@@ -1115,31 +1115,31 @@
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>3611</v>
+        <v>3337</v>
       </c>
       <c r="C20">
-        <v>38695951</v>
+        <v>49358855</v>
       </c>
       <c r="D20">
-        <v>249.3</v>
+        <v>318</v>
       </c>
       <c r="E20">
-        <v>3832095</v>
+        <v>4946582</v>
       </c>
       <c r="F20">
-        <v>47300136</v>
+        <v>61056421</v>
       </c>
       <c r="G20">
-        <v>3647623</v>
+        <v>2963721</v>
       </c>
       <c r="H20">
-        <v>17616791</v>
+        <v>14313774</v>
       </c>
       <c r="I20">
-        <v>270313</v>
+        <v>108745</v>
       </c>
       <c r="J20">
-        <v>2831</v>
+        <v>1139</v>
       </c>
       <c r="K20">
         <v>21.4</v>
@@ -1153,31 +1153,31 @@
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>3739</v>
+        <v>3420</v>
       </c>
       <c r="C21">
-        <v>5777160</v>
+        <v>7680430</v>
       </c>
       <c r="D21">
-        <v>37.1</v>
+        <v>49.4</v>
       </c>
       <c r="E21">
-        <v>102031</v>
+        <v>130397</v>
       </c>
       <c r="F21">
-        <v>1230601</v>
+        <v>1572727</v>
       </c>
       <c r="G21">
-        <v>15707082</v>
+        <v>12978483</v>
       </c>
       <c r="H21">
-        <v>73952872</v>
+        <v>61105946</v>
       </c>
       <c r="I21">
-        <v>101222</v>
+        <v>40537</v>
       </c>
       <c r="J21">
-        <v>1070</v>
+        <v>429</v>
       </c>
       <c r="K21">
         <v>101.7</v>
@@ -1191,31 +1191,31 @@
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>4072</v>
+        <v>3699</v>
       </c>
       <c r="C22">
-        <v>21186050</v>
+        <v>28123887</v>
       </c>
       <c r="D22">
-        <v>128.4</v>
+        <v>170.4</v>
       </c>
       <c r="E22">
-        <v>4932232</v>
+        <v>6397486</v>
       </c>
       <c r="F22">
-        <v>54544774</v>
+        <v>70748788</v>
       </c>
       <c r="G22">
-        <v>14993389</v>
+        <v>12275025</v>
       </c>
       <c r="H22">
-        <v>68655703</v>
+        <v>56208136</v>
       </c>
       <c r="I22">
-        <v>723386</v>
+        <v>284997</v>
       </c>
       <c r="J22">
-        <v>7515</v>
+        <v>2961</v>
       </c>
       <c r="K22">
         <v>53.1</v>
@@ -1229,31 +1229,31 @@
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>4587</v>
+        <v>3897</v>
       </c>
       <c r="C23">
-        <v>13281636</v>
+        <v>17455498</v>
       </c>
       <c r="D23">
-        <v>80.3</v>
+        <v>105.5</v>
       </c>
       <c r="E23">
-        <v>7412096</v>
+        <v>9557341</v>
       </c>
       <c r="F23">
-        <v>83290761</v>
+        <v>107397178</v>
       </c>
       <c r="G23">
-        <v>11811123</v>
+        <v>9689177</v>
       </c>
       <c r="H23">
-        <v>52483190</v>
+        <v>43054240</v>
       </c>
       <c r="I23">
-        <v>13671684</v>
+        <v>5479325</v>
       </c>
       <c r="J23">
-        <v>137683</v>
+        <v>55181</v>
       </c>
       <c r="K23">
         <v>184.2</v>
@@ -1267,31 +1267,31 @@
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>4633</v>
+        <v>3827</v>
       </c>
       <c r="C24">
-        <v>630063</v>
+        <v>802255</v>
       </c>
       <c r="D24">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="E24">
-        <v>6673569</v>
+        <v>8522986</v>
       </c>
       <c r="F24">
-        <v>78335854</v>
+        <v>100044734</v>
       </c>
       <c r="G24">
-        <v>381179</v>
+        <v>315867</v>
       </c>
       <c r="H24">
-        <v>1777235</v>
+        <v>1472719</v>
       </c>
       <c r="I24">
-        <v>15346026</v>
+        <v>6084058</v>
       </c>
       <c r="J24">
-        <v>159166</v>
+        <v>63103</v>
       </c>
       <c r="K24">
         <v>130.6</v>
@@ -1305,31 +1305,31 @@
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>4315</v>
+        <v>3622</v>
       </c>
       <c r="C25">
-        <v>16526503</v>
+        <v>21983101</v>
       </c>
       <c r="D25">
-        <v>100.4</v>
+        <v>133.6</v>
       </c>
       <c r="E25">
-        <v>123808</v>
+        <v>157911</v>
       </c>
       <c r="F25">
-        <v>1407253</v>
+        <v>1794884</v>
       </c>
       <c r="G25">
-        <v>136953</v>
+        <v>112224</v>
       </c>
       <c r="H25">
-        <v>602694</v>
+        <v>493868</v>
       </c>
       <c r="I25">
-        <v>8852251</v>
+        <v>3486311</v>
       </c>
       <c r="J25">
-        <v>92780</v>
+        <v>36540</v>
       </c>
       <c r="K25">
         <v>54.6</v>
@@ -1343,31 +1343,31 @@
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>4394</v>
+        <v>3610</v>
       </c>
       <c r="C26">
-        <v>30878156</v>
+        <v>39318805</v>
       </c>
       <c r="D26">
-        <v>184.8</v>
+        <v>235.3</v>
       </c>
       <c r="E26">
-        <v>59216</v>
+        <v>77162</v>
       </c>
       <c r="F26">
-        <v>690004</v>
+        <v>899122</v>
       </c>
       <c r="G26">
-        <v>330814</v>
+        <v>274114</v>
       </c>
       <c r="H26">
-        <v>1612340</v>
+        <v>1335993</v>
       </c>
       <c r="I26">
-        <v>17154548</v>
+        <v>6781387</v>
       </c>
       <c r="J26">
-        <v>175912</v>
+        <v>69540</v>
       </c>
       <c r="K26">
         <v>22.3</v>
@@ -1381,31 +1381,31 @@
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>3565</v>
+        <v>3206</v>
       </c>
       <c r="C27">
-        <v>30972045</v>
+        <v>39790824</v>
       </c>
       <c r="D27">
-        <v>178.8</v>
+        <v>229.7</v>
       </c>
       <c r="E27">
-        <v>13370251</v>
+        <v>17017888</v>
       </c>
       <c r="F27">
-        <v>149714558</v>
+        <v>190559283</v>
       </c>
       <c r="G27">
-        <v>365001</v>
+        <v>303856</v>
       </c>
       <c r="H27">
-        <v>1596056</v>
+        <v>1328688</v>
       </c>
       <c r="I27">
-        <v>217481</v>
+        <v>88224</v>
       </c>
       <c r="J27">
-        <v>2155</v>
+        <v>874</v>
       </c>
       <c r="K27">
         <v>86.90000000000001</v>
@@ -1419,31 +1419,31 @@
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>4016</v>
+        <v>3483</v>
       </c>
       <c r="C28">
-        <v>31686610</v>
+        <v>40806529</v>
       </c>
       <c r="D28">
-        <v>196.1</v>
+        <v>252.5</v>
       </c>
       <c r="E28">
-        <v>2421816</v>
+        <v>3173429</v>
       </c>
       <c r="F28">
-        <v>28622993</v>
+        <v>37506164</v>
       </c>
       <c r="G28">
-        <v>29297982</v>
+        <v>24317768</v>
       </c>
       <c r="H28">
-        <v>137200713</v>
+        <v>113878663</v>
       </c>
       <c r="I28">
-        <v>9522252</v>
+        <v>3769858</v>
       </c>
       <c r="J28">
-        <v>92330</v>
+        <v>36554</v>
       </c>
       <c r="K28">
         <v>21.2</v>
@@ -1457,31 +1457,31 @@
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>4170</v>
+        <v>3436</v>
       </c>
       <c r="C29">
-        <v>19656041</v>
+        <v>25727576</v>
       </c>
       <c r="D29">
-        <v>119.5</v>
+        <v>156.5</v>
       </c>
       <c r="E29">
-        <v>7152219</v>
+        <v>9132273</v>
       </c>
       <c r="F29">
-        <v>81712103</v>
+        <v>104333667</v>
       </c>
       <c r="G29">
-        <v>13640758</v>
+        <v>11164390</v>
       </c>
       <c r="H29">
-        <v>62107234</v>
+        <v>50832174</v>
       </c>
       <c r="I29">
-        <v>19981299</v>
+        <v>7884044</v>
       </c>
       <c r="J29">
-        <v>203688</v>
+        <v>80369</v>
       </c>
       <c r="K29">
         <v>123.4</v>
@@ -1495,31 +1495,31 @@
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>3935</v>
+        <v>3245</v>
       </c>
       <c r="C30">
-        <v>10260620</v>
+        <v>13509600</v>
       </c>
       <c r="D30">
-        <v>59.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E30">
-        <v>8681518</v>
+        <v>11185899</v>
       </c>
       <c r="F30">
-        <v>100112763</v>
+        <v>128992567</v>
       </c>
       <c r="G30">
-        <v>16209998</v>
+        <v>13503853</v>
       </c>
       <c r="H30">
-        <v>69801828</v>
+        <v>58148906</v>
       </c>
       <c r="I30">
-        <v>14142325</v>
+        <v>5628475</v>
       </c>
       <c r="J30">
-        <v>146822</v>
+        <v>58433</v>
       </c>
       <c r="K30">
         <v>152.3</v>
@@ -1533,31 +1533,31 @@
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>3453</v>
+        <v>3007</v>
       </c>
       <c r="C31">
-        <v>12451462</v>
+        <v>16352868</v>
       </c>
       <c r="D31">
-        <v>77</v>
+        <v>101.1</v>
       </c>
       <c r="E31">
-        <v>129482</v>
+        <v>166479</v>
       </c>
       <c r="F31">
-        <v>1463550</v>
+        <v>1881725</v>
       </c>
       <c r="G31">
-        <v>9008847</v>
+        <v>7361902</v>
       </c>
       <c r="H31">
-        <v>38851078</v>
+        <v>31748548</v>
       </c>
       <c r="I31">
-        <v>3379858</v>
+        <v>1329082</v>
       </c>
       <c r="J31">
-        <v>34096</v>
+        <v>13408</v>
       </c>
       <c r="K31">
         <v>155</v>
@@ -1571,31 +1571,31 @@
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>3962</v>
+        <v>3334</v>
       </c>
       <c r="C32">
-        <v>31400908</v>
+        <v>39918765</v>
       </c>
       <c r="D32">
-        <v>196.4</v>
+        <v>249.7</v>
       </c>
       <c r="E32">
-        <v>197247</v>
+        <v>252660</v>
       </c>
       <c r="F32">
-        <v>2159020</v>
+        <v>2765560</v>
       </c>
       <c r="G32">
-        <v>3730471</v>
+        <v>3092672</v>
       </c>
       <c r="H32">
-        <v>16593541</v>
+        <v>13756539</v>
       </c>
       <c r="I32">
-        <v>13056243</v>
+        <v>5162293</v>
       </c>
       <c r="J32">
-        <v>125423</v>
+        <v>49591</v>
       </c>
       <c r="K32">
         <v>39</v>
@@ -1609,31 +1609,31 @@
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>4488</v>
+        <v>3645</v>
       </c>
       <c r="C33">
-        <v>19027950</v>
+        <v>24850841</v>
       </c>
       <c r="D33">
-        <v>117.4</v>
+        <v>153.4</v>
       </c>
       <c r="E33">
-        <v>129272</v>
+        <v>166700</v>
       </c>
       <c r="F33">
-        <v>1372839</v>
+        <v>1770311</v>
       </c>
       <c r="G33">
-        <v>9357348</v>
+        <v>7559400</v>
       </c>
       <c r="H33">
-        <v>40963946</v>
+        <v>33093015</v>
       </c>
       <c r="I33">
-        <v>23023366</v>
+        <v>9104550</v>
       </c>
       <c r="J33">
-        <v>226171</v>
+        <v>89439</v>
       </c>
       <c r="K33">
         <v>64.5</v>
@@ -1647,31 +1647,31 @@
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>4937</v>
+        <v>4035</v>
       </c>
       <c r="C34">
-        <v>55258720</v>
+        <v>70348729</v>
       </c>
       <c r="D34">
-        <v>324.4</v>
+        <v>413</v>
       </c>
       <c r="E34">
-        <v>150885</v>
+        <v>192047</v>
       </c>
       <c r="F34">
-        <v>1686627</v>
+        <v>2146741</v>
       </c>
       <c r="G34">
-        <v>21810804</v>
+        <v>18005335</v>
       </c>
       <c r="H34">
-        <v>96852058</v>
+        <v>79953667</v>
       </c>
       <c r="I34">
-        <v>26272441</v>
+        <v>10357735</v>
       </c>
       <c r="J34">
-        <v>247348</v>
+        <v>97515</v>
       </c>
       <c r="K34">
         <v>33.9</v>
@@ -1685,31 +1685,31 @@
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>4342</v>
+        <v>3762</v>
       </c>
       <c r="C35">
-        <v>1378447</v>
+        <v>1755183</v>
       </c>
       <c r="D35">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="E35">
-        <v>136813</v>
+        <v>176913</v>
       </c>
       <c r="F35">
-        <v>1572779</v>
+        <v>2033767</v>
       </c>
       <c r="G35">
-        <v>7718740</v>
+        <v>6217752</v>
       </c>
       <c r="H35">
-        <v>31494794</v>
+        <v>25370308</v>
       </c>
       <c r="I35">
-        <v>662549</v>
+        <v>261508</v>
       </c>
       <c r="J35">
-        <v>6438</v>
+        <v>2541</v>
       </c>
       <c r="K35">
         <v>49.2</v>
@@ -1723,31 +1723,31 @@
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>5148</v>
+        <v>4206</v>
       </c>
       <c r="C36">
-        <v>48026012</v>
+        <v>61455852</v>
       </c>
       <c r="D36">
-        <v>276.9</v>
+        <v>354.3</v>
       </c>
       <c r="E36">
-        <v>2013421</v>
+        <v>2650974</v>
       </c>
       <c r="F36">
-        <v>22249909</v>
+        <v>29295379</v>
       </c>
       <c r="G36">
-        <v>21704936</v>
+        <v>18039319</v>
       </c>
       <c r="H36">
-        <v>100604397</v>
+        <v>83613925</v>
       </c>
       <c r="I36">
-        <v>32572726</v>
+        <v>12861214</v>
       </c>
       <c r="J36">
-        <v>306443</v>
+        <v>120998</v>
       </c>
       <c r="K36">
         <v>31.2</v>
@@ -1761,31 +1761,31 @@
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>4507</v>
+        <v>3969</v>
       </c>
       <c r="C37">
-        <v>64854176</v>
+        <v>82193967</v>
       </c>
       <c r="D37">
-        <v>367.4</v>
+        <v>465.6</v>
       </c>
       <c r="E37">
-        <v>227248</v>
+        <v>289684</v>
       </c>
       <c r="F37">
-        <v>2370112</v>
+        <v>3021284</v>
       </c>
       <c r="G37">
-        <v>11496632</v>
+        <v>9516344</v>
       </c>
       <c r="H37">
-        <v>48127765</v>
+        <v>39837786</v>
       </c>
       <c r="I37">
-        <v>181215</v>
+        <v>72132</v>
       </c>
       <c r="J37">
-        <v>1708</v>
+        <v>680</v>
       </c>
       <c r="K37">
         <v>74.2</v>
@@ -1799,31 +1799,31 @@
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>4410</v>
+        <v>3832</v>
       </c>
       <c r="C38">
-        <v>25217014</v>
+        <v>32468363</v>
       </c>
       <c r="D38">
-        <v>141.4</v>
+        <v>182</v>
       </c>
       <c r="E38">
-        <v>88812</v>
+        <v>115032</v>
       </c>
       <c r="F38">
-        <v>988294</v>
+        <v>1280066</v>
       </c>
       <c r="G38">
-        <v>9353272</v>
+        <v>7597400</v>
       </c>
       <c r="H38">
-        <v>41760736</v>
+        <v>33921073</v>
       </c>
       <c r="I38">
-        <v>8762412</v>
+        <v>3467971</v>
       </c>
       <c r="J38">
-        <v>83058</v>
+        <v>32872</v>
       </c>
       <c r="K38">
         <v>28.1</v>
@@ -1837,31 +1837,31 @@
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>4473</v>
+        <v>3670</v>
       </c>
       <c r="C39">
-        <v>234469</v>
+        <v>312420</v>
       </c>
       <c r="D39">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="E39">
-        <v>13998037</v>
+        <v>17816159</v>
       </c>
       <c r="F39">
-        <v>146892970</v>
+        <v>186959684</v>
       </c>
       <c r="G39">
-        <v>5263341</v>
+        <v>4221243</v>
       </c>
       <c r="H39">
-        <v>22492224</v>
+        <v>18038952</v>
       </c>
       <c r="I39">
-        <v>26621650</v>
+        <v>10529343</v>
       </c>
       <c r="J39">
-        <v>248923</v>
+        <v>98453</v>
       </c>
       <c r="K39">
         <v>91.40000000000001</v>
@@ -1875,31 +1875,31 @@
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>3985</v>
+        <v>3347</v>
       </c>
       <c r="C40">
-        <v>16505715</v>
+        <v>21141593</v>
       </c>
       <c r="D40">
-        <v>93.90000000000001</v>
+        <v>120.2</v>
       </c>
       <c r="E40">
-        <v>8549553</v>
+        <v>10897326</v>
       </c>
       <c r="F40">
-        <v>94286874</v>
+        <v>120178769</v>
       </c>
       <c r="G40">
-        <v>12480343</v>
+        <v>10188105</v>
       </c>
       <c r="H40">
-        <v>51930430</v>
+        <v>42392478</v>
       </c>
       <c r="I40">
-        <v>10177598</v>
+        <v>4172223</v>
       </c>
       <c r="J40">
-        <v>99188</v>
+        <v>40661</v>
       </c>
       <c r="K40">
         <v>117</v>
@@ -1913,31 +1913,31 @@
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>4008</v>
+        <v>3285</v>
       </c>
       <c r="C41">
-        <v>15333760</v>
+        <v>19972476</v>
       </c>
       <c r="D41">
-        <v>89</v>
+        <v>115.9</v>
       </c>
       <c r="E41">
-        <v>6925969</v>
+        <v>8984781</v>
       </c>
       <c r="F41">
-        <v>76834199</v>
+        <v>99673922</v>
       </c>
       <c r="G41">
-        <v>5351055</v>
+        <v>4367559</v>
       </c>
       <c r="H41">
-        <v>23436611</v>
+        <v>19129084</v>
       </c>
       <c r="I41">
-        <v>20629217</v>
+        <v>8213308</v>
       </c>
       <c r="J41">
-        <v>191338</v>
+        <v>76179</v>
       </c>
       <c r="K41">
         <v>31.2</v>
@@ -1951,31 +1951,31 @@
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>3201</v>
+        <v>2845</v>
       </c>
       <c r="C42">
-        <v>7955123</v>
+        <v>10449100</v>
       </c>
       <c r="D42">
-        <v>45.1</v>
+        <v>59.2</v>
       </c>
       <c r="E42">
-        <v>8754392</v>
+        <v>11215430</v>
       </c>
       <c r="F42">
-        <v>95991790</v>
+        <v>122977040</v>
       </c>
       <c r="G42">
-        <v>15950634</v>
+        <v>13254715</v>
       </c>
       <c r="H42">
-        <v>65639233</v>
+        <v>54545124</v>
       </c>
       <c r="I42">
-        <v>513786</v>
+        <v>202771</v>
       </c>
       <c r="J42">
-        <v>5125</v>
+        <v>2023</v>
       </c>
       <c r="K42">
         <v>167.9</v>
@@ -1989,31 +1989,31 @@
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>3925</v>
+        <v>3211</v>
       </c>
       <c r="C43">
-        <v>39049480</v>
+        <v>49467719</v>
       </c>
       <c r="D43">
-        <v>217.5</v>
+        <v>275.5</v>
       </c>
       <c r="E43">
-        <v>10213931</v>
+        <v>13011028</v>
       </c>
       <c r="F43">
-        <v>110786613</v>
+        <v>141125658</v>
       </c>
       <c r="G43">
-        <v>7885802</v>
+        <v>6475652</v>
       </c>
       <c r="H43">
-        <v>33548669</v>
+        <v>27549451</v>
       </c>
       <c r="I43">
-        <v>22939468</v>
+        <v>9054492</v>
       </c>
       <c r="J43">
-        <v>228868</v>
+        <v>90337</v>
       </c>
       <c r="K43">
         <v>154.4</v>
@@ -2027,31 +2027,31 @@
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>3832</v>
+        <v>3260</v>
       </c>
       <c r="C44">
-        <v>38906578</v>
+        <v>50132962</v>
       </c>
       <c r="D44">
-        <v>215.5</v>
+        <v>277.6</v>
       </c>
       <c r="E44">
-        <v>64751</v>
+        <v>86221</v>
       </c>
       <c r="F44">
-        <v>698753</v>
+        <v>930440</v>
       </c>
       <c r="G44">
-        <v>158076</v>
+        <v>126938</v>
       </c>
       <c r="H44">
-        <v>679750</v>
+        <v>545854</v>
       </c>
       <c r="I44">
-        <v>8673191</v>
+        <v>3483046</v>
       </c>
       <c r="J44">
-        <v>84985</v>
+        <v>34129</v>
       </c>
       <c r="K44">
         <v>58.7</v>
@@ -2065,31 +2065,31 @@
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>4348</v>
+        <v>3573</v>
       </c>
       <c r="C45">
-        <v>42553917</v>
+        <v>54196166</v>
       </c>
       <c r="D45">
-        <v>240.5</v>
+        <v>306.3</v>
       </c>
       <c r="E45">
-        <v>6089419</v>
+        <v>7813778</v>
       </c>
       <c r="F45">
-        <v>65216929</v>
+        <v>83684607</v>
       </c>
       <c r="G45">
-        <v>1196359</v>
+        <v>957087</v>
       </c>
       <c r="H45">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="I45">
-        <v>27514241</v>
+        <v>10862254</v>
       </c>
       <c r="J45">
-        <v>262516</v>
+        <v>103638</v>
       </c>
       <c r="K45">
         <v>30.9</v>
@@ -2103,31 +2103,31 @@
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>4837</v>
+        <v>3944</v>
       </c>
       <c r="C46">
-        <v>26467819</v>
+        <v>34450803</v>
       </c>
       <c r="D46">
-        <v>150.9</v>
+        <v>196.3</v>
       </c>
       <c r="E46">
-        <v>8266377</v>
+        <v>10552334</v>
       </c>
       <c r="F46">
-        <v>87304716</v>
+        <v>111447680</v>
       </c>
       <c r="G46">
-        <v>14216167</v>
+        <v>11527577</v>
       </c>
       <c r="H46">
-        <v>57238229</v>
+        <v>46413221</v>
       </c>
       <c r="I46">
-        <v>37581679</v>
+        <v>14905684</v>
       </c>
       <c r="J46">
-        <v>348196</v>
+        <v>138102</v>
       </c>
       <c r="K46">
         <v>41.6</v>
@@ -2141,31 +2141,31 @@
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>5022</v>
+        <v>4141</v>
       </c>
       <c r="C47">
-        <v>15363420</v>
+        <v>20569130</v>
       </c>
       <c r="D47">
-        <v>86.8</v>
+        <v>116.2</v>
       </c>
       <c r="E47">
-        <v>5143909</v>
+        <v>6776853</v>
       </c>
       <c r="F47">
-        <v>53212722</v>
+        <v>70105208</v>
       </c>
       <c r="G47">
-        <v>25026533</v>
+        <v>20662871</v>
       </c>
       <c r="H47">
-        <v>102706402</v>
+        <v>84798366</v>
       </c>
       <c r="I47">
-        <v>17524258</v>
+        <v>6905069</v>
       </c>
       <c r="J47">
-        <v>161378</v>
+        <v>63588</v>
       </c>
       <c r="K47">
         <v>47.1</v>
@@ -2179,31 +2179,31 @@
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>4549</v>
+        <v>4028</v>
       </c>
       <c r="C48">
-        <v>56999890</v>
+        <v>72224969</v>
       </c>
       <c r="D48">
-        <v>318.9</v>
+        <v>404</v>
       </c>
       <c r="E48">
-        <v>130882</v>
+        <v>168238</v>
       </c>
       <c r="F48">
-        <v>1385476</v>
+        <v>1780919</v>
       </c>
       <c r="G48">
-        <v>15982215</v>
+        <v>13290991</v>
       </c>
       <c r="H48">
-        <v>68224749</v>
+        <v>56736474</v>
       </c>
       <c r="I48">
-        <v>811565</v>
+        <v>319366</v>
       </c>
       <c r="J48">
-        <v>7752</v>
+        <v>3051</v>
       </c>
       <c r="K48">
         <v>57.4</v>
@@ -2217,31 +2217,31 @@
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>4153</v>
+        <v>3783</v>
       </c>
       <c r="C49">
-        <v>42178024</v>
+        <v>53679838</v>
       </c>
       <c r="D49">
-        <v>226.2</v>
+        <v>287.9</v>
       </c>
       <c r="E49">
-        <v>238241</v>
+        <v>306200</v>
       </c>
       <c r="F49">
-        <v>2431521</v>
+        <v>3125126</v>
       </c>
       <c r="G49">
-        <v>3690999</v>
+        <v>3024829</v>
       </c>
       <c r="H49">
-        <v>15076223</v>
+        <v>12355191</v>
       </c>
       <c r="I49">
-        <v>321981</v>
+        <v>127916</v>
       </c>
       <c r="J49">
-        <v>3002</v>
+        <v>1193</v>
       </c>
       <c r="K49">
         <v>82.8</v>

--- a/tools/synthetic_pilots/synth_real_estate.xlsx
+++ b/tools/synthetic_pilots/synth_real_estate.xlsx
@@ -431,7 +431,7 @@
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>3119</v>
+        <v>3161</v>
       </c>
       <c r="C2">
         <v>29844516</v>
@@ -469,7 +469,7 @@
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>3472</v>
+        <v>3435</v>
       </c>
       <c r="C3">
         <v>39553551</v>
@@ -507,7 +507,7 @@
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>3406</v>
+        <v>3366</v>
       </c>
       <c r="C4">
         <v>63633078</v>
@@ -545,7 +545,7 @@
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>3122</v>
+        <v>3138</v>
       </c>
       <c r="C5">
         <v>1155981</v>
@@ -583,7 +583,7 @@
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>3297</v>
+        <v>3319</v>
       </c>
       <c r="C6">
         <v>24832268</v>
@@ -621,7 +621,7 @@
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>3459</v>
+        <v>3375</v>
       </c>
       <c r="C7">
         <v>61565865</v>
@@ -659,7 +659,7 @@
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>3458</v>
+        <v>3406</v>
       </c>
       <c r="C8">
         <v>983518</v>
@@ -697,7 +697,7 @@
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>3622</v>
+        <v>3646</v>
       </c>
       <c r="C9">
         <v>1017627</v>
@@ -735,7 +735,7 @@
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>3677</v>
+        <v>3622</v>
       </c>
       <c r="C10">
         <v>37022398</v>
@@ -773,7 +773,7 @@
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>4120</v>
+        <v>4087</v>
       </c>
       <c r="C11">
         <v>62447095</v>
@@ -811,7 +811,7 @@
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>4270</v>
+        <v>4159</v>
       </c>
       <c r="C12">
         <v>53817786</v>
@@ -849,7 +849,7 @@
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>3927</v>
+        <v>3975</v>
       </c>
       <c r="C13">
         <v>936128</v>
@@ -887,7 +887,7 @@
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>3611</v>
+        <v>3538</v>
       </c>
       <c r="C14">
         <v>1401881</v>
@@ -925,7 +925,7 @@
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>3708</v>
+        <v>3724</v>
       </c>
       <c r="C15">
         <v>46856851</v>
@@ -963,7 +963,7 @@
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>3463</v>
+        <v>3539</v>
       </c>
       <c r="C16">
         <v>66502798</v>
@@ -1001,7 +1001,7 @@
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="C17">
         <v>422188</v>
@@ -1039,7 +1039,7 @@
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>3169</v>
+        <v>3233</v>
       </c>
       <c r="C18">
         <v>40872977</v>
@@ -1077,7 +1077,7 @@
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="C19">
         <v>55500061</v>
@@ -1115,7 +1115,7 @@
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>3337</v>
+        <v>3283</v>
       </c>
       <c r="C20">
         <v>49358855</v>
@@ -1153,7 +1153,7 @@
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>3420</v>
+        <v>3367</v>
       </c>
       <c r="C21">
         <v>7680430</v>
@@ -1191,7 +1191,7 @@
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>3699</v>
+        <v>3684</v>
       </c>
       <c r="C22">
         <v>28123887</v>
@@ -1229,7 +1229,7 @@
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>3897</v>
+        <v>3975</v>
       </c>
       <c r="C23">
         <v>17455498</v>
@@ -1267,7 +1267,7 @@
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>3827</v>
+        <v>3912</v>
       </c>
       <c r="C24">
         <v>802255</v>
@@ -1305,7 +1305,7 @@
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>3622</v>
+        <v>3635</v>
       </c>
       <c r="C25">
         <v>21983101</v>
@@ -1343,7 +1343,7 @@
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>3610</v>
+        <v>3657</v>
       </c>
       <c r="C26">
         <v>39318805</v>
@@ -1381,7 +1381,7 @@
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>3206</v>
+        <v>3243</v>
       </c>
       <c r="C27">
         <v>39790824</v>
@@ -1419,7 +1419,7 @@
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>3483</v>
+        <v>3401</v>
       </c>
       <c r="C28">
         <v>40806529</v>
@@ -1457,7 +1457,7 @@
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>3436</v>
+        <v>3479</v>
       </c>
       <c r="C29">
         <v>25727576</v>
@@ -1495,7 +1495,7 @@
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>3245</v>
+        <v>3202</v>
       </c>
       <c r="C30">
         <v>13509600</v>
@@ -1533,7 +1533,7 @@
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>3007</v>
+        <v>2972</v>
       </c>
       <c r="C31">
         <v>16352868</v>
@@ -1571,7 +1571,7 @@
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>3334</v>
+        <v>3344</v>
       </c>
       <c r="C32">
         <v>39918765</v>
@@ -1609,7 +1609,7 @@
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>3645</v>
+        <v>3807</v>
       </c>
       <c r="C33">
         <v>24850841</v>
@@ -1647,7 +1647,7 @@
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="C34">
         <v>70348729</v>
@@ -1685,7 +1685,7 @@
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>3762</v>
+        <v>3803</v>
       </c>
       <c r="C35">
         <v>1755183</v>
@@ -1723,7 +1723,7 @@
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>4206</v>
+        <v>4143</v>
       </c>
       <c r="C36">
         <v>61455852</v>
@@ -1761,7 +1761,7 @@
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>3969</v>
+        <v>4006</v>
       </c>
       <c r="C37">
         <v>82193967</v>
@@ -1799,7 +1799,7 @@
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>3832</v>
+        <v>3837</v>
       </c>
       <c r="C38">
         <v>32468363</v>
@@ -1837,7 +1837,7 @@
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>3670</v>
+        <v>3675</v>
       </c>
       <c r="C39">
         <v>312420</v>
@@ -1875,7 +1875,7 @@
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>3347</v>
+        <v>3294</v>
       </c>
       <c r="C40">
         <v>21141593</v>
@@ -1913,7 +1913,7 @@
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>3285</v>
+        <v>3267</v>
       </c>
       <c r="C41">
         <v>19972476</v>
@@ -1951,7 +1951,7 @@
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>2845</v>
+        <v>2780</v>
       </c>
       <c r="C42">
         <v>10449100</v>
@@ -1989,7 +1989,7 @@
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>3211</v>
+        <v>3178</v>
       </c>
       <c r="C43">
         <v>49467719</v>
@@ -2027,7 +2027,7 @@
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>3260</v>
+        <v>3231</v>
       </c>
       <c r="C44">
         <v>50132962</v>
@@ -2065,7 +2065,7 @@
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>3573</v>
+        <v>3504</v>
       </c>
       <c r="C45">
         <v>54196166</v>
@@ -2103,7 +2103,7 @@
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>3944</v>
+        <v>3955</v>
       </c>
       <c r="C46">
         <v>34450803</v>
@@ -2141,7 +2141,7 @@
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>4141</v>
+        <v>4190</v>
       </c>
       <c r="C47">
         <v>20569130</v>
@@ -2179,7 +2179,7 @@
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>4028</v>
+        <v>4108</v>
       </c>
       <c r="C48">
         <v>72224969</v>
@@ -2217,7 +2217,7 @@
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>3783</v>
+        <v>3903</v>
       </c>
       <c r="C49">
         <v>53679838</v>
